--- a/class_diagram/model/form/manager/成績管理sys_クラス図_model_form_manager.xlsx
+++ b/class_diagram/model/form/manager/成績管理sys_クラス図_model_form_manager.xlsx
@@ -1,15 +1,17 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29530"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29609"/>
   <workbookPr/>
-  <xr:revisionPtr revIDLastSave="133" documentId="11_3F8216BDF2DCCE836B02CE998F0AE45F5E522874" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{35C50182-6A5E-4DB3-8B14-E71EFA45601C}"/>
+  <xr:revisionPtr revIDLastSave="140" documentId="11_3F8216BDF2DCCE836B02CE998F0AE45F5E522874" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1786B710-7EA7-476A-9514-53B5BB859F50}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" firstSheet="1" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="MajorSetForm" sheetId="3" r:id="rId1"/>
-    <sheet name="MajorRegisterForm" sheetId="2" r:id="rId2"/>
+    <sheet name="SubjectSetForm" sheetId="4" r:id="rId1"/>
+    <sheet name="SubjectRegisterForm" sheetId="5" r:id="rId2"/>
+    <sheet name="MajorSetForm" sheetId="3" r:id="rId3"/>
+    <sheet name="MajorRegisterForm" sheetId="2" r:id="rId4"/>
   </sheets>
   <calcPr calcId="191028"/>
   <extLst>
@@ -101,6 +103,840 @@
         <xdr:cNvPr id="2" name="角丸四角形 2">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8B218C94-0E43-4F62-A16D-2582E08F6B6D}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="590550" y="1057275"/>
+          <a:ext cx="11096625" cy="3257550"/>
+        </a:xfrm>
+        <a:prstGeom prst="roundRect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="bg2">
+            <a:lumMod val="90000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr spcFirstLastPara="0" vertOverflow="clip" horzOverflow="clip" wrap="square" lIns="91440" tIns="45720" rIns="91440" bIns="45720" rtlCol="0" anchor="t">
+          <a:noAutofit/>
+        </a:bodyPr>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr marL="0" indent="0" algn="l"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="3600" b="0" i="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="75000"/>
+                  <a:lumOff val="25000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="Aptos Narrow" panose="020B0004020202020204" pitchFamily="34" charset="0"/>
+            </a:rPr>
+            <a:t>SubjectSetForm</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>352425</xdr:colOff>
+      <xdr:row>13</xdr:row>
+      <xdr:rowOff>19050</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>438150</xdr:colOff>
+      <xdr:row>15</xdr:row>
+      <xdr:rowOff>19050</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="3" name="四角形 6">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{687B1D3D-2301-4FCE-8E88-742118CC7404}"/>
+            </a:ext>
+            <a:ext uri="{147F2762-F138-4A5C-976F-8EAC2B608ADB}">
+              <a16:predDERef xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" pred="{8B218C94-0E43-4F62-A16D-2582E08F6B6D}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1724025" y="2619375"/>
+          <a:ext cx="1457325" cy="400050"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr rot="0" spcFirstLastPara="0" vert="horz" wrap="square" lIns="91440" tIns="45720" rIns="91440" bIns="45720" numCol="1" spcCol="0" rtlCol="0" fromWordArt="0" anchor="t" anchorCtr="0" forceAA="0" compatLnSpc="1">
+          <a:prstTxWarp prst="textNoShape">
+            <a:avLst/>
+          </a:prstTxWarp>
+          <a:noAutofit/>
+        </a:bodyPr>
+        <a:lstStyle>
+          <a:lvl1pPr marL="0" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl1pPr>
+          <a:lvl2pPr marL="457200" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl2pPr>
+          <a:lvl3pPr marL="914400" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl3pPr>
+          <a:lvl4pPr marL="1371600" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl4pPr>
+          <a:lvl5pPr marL="1828800" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl5pPr>
+          <a:lvl6pPr marL="2286000" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl6pPr>
+          <a:lvl7pPr marL="2743200" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl7pPr>
+          <a:lvl8pPr marL="3200400" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl8pPr>
+          <a:lvl9pPr marL="3657600" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl9pPr>
+        </a:lstStyle>
+        <a:p>
+          <a:pPr marL="0" indent="0" algn="ctr"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="1600" b="0" i="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="Aptos Narrow" panose="020B0004020202020204" pitchFamily="34" charset="0"/>
+            </a:rPr>
+            <a:t>name : String</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>9525</xdr:colOff>
+      <xdr:row>13</xdr:row>
+      <xdr:rowOff>9525</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>95250</xdr:colOff>
+      <xdr:row>15</xdr:row>
+      <xdr:rowOff>9525</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="4" name="四角形 7">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{274DC5DE-03DE-4438-90CD-206CF4EC3B5F}"/>
+            </a:ext>
+            <a:ext uri="{147F2762-F138-4A5C-976F-8EAC2B608ADB}">
+              <a16:predDERef xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" pred="{687B1D3D-2301-4FCE-8E88-742118CC7404}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="3438525" y="2609850"/>
+          <a:ext cx="1457325" cy="400050"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr rot="0" spcFirstLastPara="0" vert="horz" wrap="square" lIns="91440" tIns="45720" rIns="91440" bIns="45720" numCol="1" spcCol="0" rtlCol="0" fromWordArt="0" anchor="t" anchorCtr="0" forceAA="0" compatLnSpc="1">
+          <a:prstTxWarp prst="textNoShape">
+            <a:avLst/>
+          </a:prstTxWarp>
+          <a:noAutofit/>
+        </a:bodyPr>
+        <a:lstStyle>
+          <a:lvl1pPr marL="0" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl1pPr>
+          <a:lvl2pPr marL="457200" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl2pPr>
+          <a:lvl3pPr marL="914400" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl3pPr>
+          <a:lvl4pPr marL="1371600" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl4pPr>
+          <a:lvl5pPr marL="1828800" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl5pPr>
+          <a:lvl6pPr marL="2286000" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl6pPr>
+          <a:lvl7pPr marL="2743200" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl7pPr>
+          <a:lvl8pPr marL="3200400" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl8pPr>
+          <a:lvl9pPr marL="3657600" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl9pPr>
+        </a:lstStyle>
+        <a:p>
+          <a:pPr marL="0" indent="0" algn="ctr"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="1600" b="0" i="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="Aptos Narrow" panose="020B0004020202020204" pitchFamily="34" charset="0"/>
+            </a:rPr>
+            <a:t>kana : String</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>590550</xdr:colOff>
+      <xdr:row>5</xdr:row>
+      <xdr:rowOff>57150</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>17</xdr:col>
+      <xdr:colOff>28575</xdr:colOff>
+      <xdr:row>21</xdr:row>
+      <xdr:rowOff>114300</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="2" name="角丸四角形 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B48273B0-0D80-4560-821D-964413218312}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="590550" y="1057275"/>
+          <a:ext cx="11096625" cy="3257550"/>
+        </a:xfrm>
+        <a:prstGeom prst="roundRect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="bg2">
+            <a:lumMod val="90000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr spcFirstLastPara="0" vertOverflow="clip" horzOverflow="clip" wrap="square" lIns="91440" tIns="45720" rIns="91440" bIns="45720" rtlCol="0" anchor="t">
+          <a:noAutofit/>
+        </a:bodyPr>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr marL="0" indent="0" algn="l"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="3600" b="0" i="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="75000"/>
+                  <a:lumOff val="25000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="Aptos Narrow" panose="020B0004020202020204" pitchFamily="34" charset="0"/>
+            </a:rPr>
+            <a:t>SubjectRegisterForm</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>352425</xdr:colOff>
+      <xdr:row>13</xdr:row>
+      <xdr:rowOff>19050</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>438150</xdr:colOff>
+      <xdr:row>15</xdr:row>
+      <xdr:rowOff>19050</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="3" name="四角形 6">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E9EF4880-C941-4D25-A5C1-2DE66B81B09D}"/>
+            </a:ext>
+            <a:ext uri="{147F2762-F138-4A5C-976F-8EAC2B608ADB}">
+              <a16:predDERef xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" pred="{B48273B0-0D80-4560-821D-964413218312}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1724025" y="2619375"/>
+          <a:ext cx="1457325" cy="400050"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr rot="0" spcFirstLastPara="0" vert="horz" wrap="square" lIns="91440" tIns="45720" rIns="91440" bIns="45720" numCol="1" spcCol="0" rtlCol="0" fromWordArt="0" anchor="t" anchorCtr="0" forceAA="0" compatLnSpc="1">
+          <a:prstTxWarp prst="textNoShape">
+            <a:avLst/>
+          </a:prstTxWarp>
+          <a:noAutofit/>
+        </a:bodyPr>
+        <a:lstStyle>
+          <a:lvl1pPr marL="0" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl1pPr>
+          <a:lvl2pPr marL="457200" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl2pPr>
+          <a:lvl3pPr marL="914400" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl3pPr>
+          <a:lvl4pPr marL="1371600" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl4pPr>
+          <a:lvl5pPr marL="1828800" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl5pPr>
+          <a:lvl6pPr marL="2286000" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl6pPr>
+          <a:lvl7pPr marL="2743200" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl7pPr>
+          <a:lvl8pPr marL="3200400" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl8pPr>
+          <a:lvl9pPr marL="3657600" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl9pPr>
+        </a:lstStyle>
+        <a:p>
+          <a:pPr marL="0" indent="0" algn="ctr"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="1600" b="0" i="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="Aptos Narrow" panose="020B0004020202020204" pitchFamily="34" charset="0"/>
+            </a:rPr>
+            <a:t>name : String</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>9525</xdr:colOff>
+      <xdr:row>13</xdr:row>
+      <xdr:rowOff>9525</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>95250</xdr:colOff>
+      <xdr:row>15</xdr:row>
+      <xdr:rowOff>9525</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="4" name="四角形 7">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4B191700-9C45-425D-8E44-36B5F2757292}"/>
+            </a:ext>
+            <a:ext uri="{147F2762-F138-4A5C-976F-8EAC2B608ADB}">
+              <a16:predDERef xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" pred="{E9EF4880-C941-4D25-A5C1-2DE66B81B09D}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="3438525" y="2609850"/>
+          <a:ext cx="1457325" cy="400050"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr rot="0" spcFirstLastPara="0" vert="horz" wrap="square" lIns="91440" tIns="45720" rIns="91440" bIns="45720" numCol="1" spcCol="0" rtlCol="0" fromWordArt="0" anchor="t" anchorCtr="0" forceAA="0" compatLnSpc="1">
+          <a:prstTxWarp prst="textNoShape">
+            <a:avLst/>
+          </a:prstTxWarp>
+          <a:noAutofit/>
+        </a:bodyPr>
+        <a:lstStyle>
+          <a:lvl1pPr marL="0" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl1pPr>
+          <a:lvl2pPr marL="457200" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl2pPr>
+          <a:lvl3pPr marL="914400" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl3pPr>
+          <a:lvl4pPr marL="1371600" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl4pPr>
+          <a:lvl5pPr marL="1828800" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl5pPr>
+          <a:lvl6pPr marL="2286000" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl6pPr>
+          <a:lvl7pPr marL="2743200" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl7pPr>
+          <a:lvl8pPr marL="3200400" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl8pPr>
+          <a:lvl9pPr marL="3657600" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl9pPr>
+        </a:lstStyle>
+        <a:p>
+          <a:pPr marL="0" indent="0" algn="ctr"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="1600" b="0" i="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="Aptos Narrow" panose="020B0004020202020204" pitchFamily="34" charset="0"/>
+            </a:rPr>
+            <a:t>kana : String</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>590550</xdr:colOff>
+      <xdr:row>5</xdr:row>
+      <xdr:rowOff>57150</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>17</xdr:col>
+      <xdr:colOff>28575</xdr:colOff>
+      <xdr:row>21</xdr:row>
+      <xdr:rowOff>114300</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="2" name="角丸四角形 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
               <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{AA1A054E-C2B2-4E17-929A-94B45370BA6B}"/>
             </a:ext>
           </a:extLst>
@@ -498,7 +1334,7 @@
 </xdr:wsDr>
 </file>
 
-<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/drawings/drawing4.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
@@ -1231,6 +2067,26 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{97A4F957-B88B-4361-B99C-701B3EAF90A9}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15.75"/>
+  <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{185333AE-AB74-4976-8C77-888F8A00E05F}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15.75"/>
+  <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5B731B65-5929-44EB-B7D4-473FCCD2560E}">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="15.75"/>
@@ -1240,7 +2096,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{63A8633E-387F-40CD-BD90-4057C77280B7}">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="15.75"/>

--- a/class_diagram/model/form/manager/成績管理sys_クラス図_model_form_manager.xlsx
+++ b/class_diagram/model/form/manager/成績管理sys_クラス図_model_form_manager.xlsx
@@ -3,15 +3,17 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29609"/>
   <workbookPr/>
-  <xr:revisionPtr revIDLastSave="140" documentId="11_3F8216BDF2DCCE836B02CE998F0AE45F5E522874" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1786B710-7EA7-476A-9514-53B5BB859F50}"/>
+  <xr:revisionPtr revIDLastSave="155" documentId="11_3F8216BDF2DCCE836B02CE998F0AE45F5E522874" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{79943971-9108-4909-AC09-B951A49801E4}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" firstSheet="1" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" firstSheet="3" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="SubjectSetForm" sheetId="4" r:id="rId1"/>
     <sheet name="SubjectRegisterForm" sheetId="5" r:id="rId2"/>
     <sheet name="MajorSetForm" sheetId="3" r:id="rId3"/>
     <sheet name="MajorRegisterForm" sheetId="2" r:id="rId4"/>
+    <sheet name="ClassSetForm" sheetId="7" r:id="rId5"/>
+    <sheet name="ClassRegisterForm" sheetId="6" r:id="rId6"/>
   </sheets>
   <calcPr calcId="191028"/>
   <extLst>
@@ -1742,6 +1744,840 @@
               <a:latin typeface="Aptos Narrow" panose="020B0004020202020204" pitchFamily="34" charset="0"/>
             </a:rPr>
             <a:t>kana : String</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing5.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>676275</xdr:colOff>
+      <xdr:row>5</xdr:row>
+      <xdr:rowOff>104775</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>17</xdr:col>
+      <xdr:colOff>114300</xdr:colOff>
+      <xdr:row>21</xdr:row>
+      <xdr:rowOff>161925</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="2" name="角丸四角形 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00C17359-9A90-49BC-BBF4-28A43125B716}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="676275" y="1104900"/>
+          <a:ext cx="11096625" cy="3257550"/>
+        </a:xfrm>
+        <a:prstGeom prst="roundRect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="bg2">
+            <a:lumMod val="90000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr spcFirstLastPara="0" vertOverflow="clip" horzOverflow="clip" wrap="square" lIns="91440" tIns="45720" rIns="91440" bIns="45720" rtlCol="0" anchor="t">
+          <a:noAutofit/>
+        </a:bodyPr>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr marL="0" indent="0" algn="l"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="3600" b="0" i="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="75000"/>
+                  <a:lumOff val="25000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="Aptos Narrow" panose="020B0004020202020204" pitchFamily="34" charset="0"/>
+            </a:rPr>
+            <a:t>ClassSetForm</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>352425</xdr:colOff>
+      <xdr:row>13</xdr:row>
+      <xdr:rowOff>19050</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>666750</xdr:colOff>
+      <xdr:row>15</xdr:row>
+      <xdr:rowOff>19050</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="3" name="四角形 6">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D0CCD0E6-B287-448C-ADA7-C2A19C1D7F52}"/>
+            </a:ext>
+            <a:ext uri="{147F2762-F138-4A5C-976F-8EAC2B608ADB}">
+              <a16:predDERef xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" pred="{00C17359-9A90-49BC-BBF4-28A43125B716}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1724025" y="2619375"/>
+          <a:ext cx="1685925" cy="400050"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr rot="0" spcFirstLastPara="0" vert="horz" wrap="square" lIns="91440" tIns="45720" rIns="91440" bIns="45720" numCol="1" spcCol="0" rtlCol="0" fromWordArt="0" anchor="t" anchorCtr="0" forceAA="0" compatLnSpc="1">
+          <a:prstTxWarp prst="textNoShape">
+            <a:avLst/>
+          </a:prstTxWarp>
+          <a:noAutofit/>
+        </a:bodyPr>
+        <a:lstStyle>
+          <a:lvl1pPr marL="0" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl1pPr>
+          <a:lvl2pPr marL="457200" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl2pPr>
+          <a:lvl3pPr marL="914400" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl3pPr>
+          <a:lvl4pPr marL="1371600" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl4pPr>
+          <a:lvl5pPr marL="1828800" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl5pPr>
+          <a:lvl6pPr marL="2286000" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl6pPr>
+          <a:lvl7pPr marL="2743200" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl7pPr>
+          <a:lvl8pPr marL="3200400" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl8pPr>
+          <a:lvl9pPr marL="3657600" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl9pPr>
+        </a:lstStyle>
+        <a:p>
+          <a:pPr marL="0" indent="0" algn="ctr"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="1600" b="0" i="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="Aptos Narrow" panose="020B0004020202020204" pitchFamily="34" charset="0"/>
+            </a:rPr>
+            <a:t>startYear : int</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>295275</xdr:colOff>
+      <xdr:row>13</xdr:row>
+      <xdr:rowOff>9525</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>381000</xdr:colOff>
+      <xdr:row>15</xdr:row>
+      <xdr:rowOff>9525</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="4" name="四角形 7">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9BD32B3E-78C7-4F63-8B98-688F329EB388}"/>
+            </a:ext>
+            <a:ext uri="{147F2762-F138-4A5C-976F-8EAC2B608ADB}">
+              <a16:predDERef xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" pred="{D0CCD0E6-B287-448C-ADA7-C2A19C1D7F52}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="3724275" y="2609850"/>
+          <a:ext cx="2143125" cy="400050"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr rot="0" spcFirstLastPara="0" vert="horz" wrap="square" lIns="91440" tIns="45720" rIns="91440" bIns="45720" numCol="1" spcCol="0" rtlCol="0" fromWordArt="0" anchor="t" anchorCtr="0" forceAA="0" compatLnSpc="1">
+          <a:prstTxWarp prst="textNoShape">
+            <a:avLst/>
+          </a:prstTxWarp>
+          <a:noAutofit/>
+        </a:bodyPr>
+        <a:lstStyle>
+          <a:lvl1pPr marL="0" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl1pPr>
+          <a:lvl2pPr marL="457200" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl2pPr>
+          <a:lvl3pPr marL="914400" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl3pPr>
+          <a:lvl4pPr marL="1371600" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl4pPr>
+          <a:lvl5pPr marL="1828800" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl5pPr>
+          <a:lvl6pPr marL="2286000" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl6pPr>
+          <a:lvl7pPr marL="2743200" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl7pPr>
+          <a:lvl8pPr marL="3200400" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl8pPr>
+          <a:lvl9pPr marL="3657600" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl9pPr>
+        </a:lstStyle>
+        <a:p>
+          <a:pPr marL="0" indent="0" algn="ctr"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="1600" b="0" i="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="Aptos Narrow" panose="020B0004020202020204" pitchFamily="34" charset="0"/>
+            </a:rPr>
+            <a:t>majorName : String</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing6.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>676275</xdr:colOff>
+      <xdr:row>5</xdr:row>
+      <xdr:rowOff>104775</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>17</xdr:col>
+      <xdr:colOff>114300</xdr:colOff>
+      <xdr:row>21</xdr:row>
+      <xdr:rowOff>161925</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="2" name="角丸四角形 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{585451F5-6F59-4D89-9C42-34BC080AF344}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="676275" y="1104900"/>
+          <a:ext cx="11096625" cy="3257550"/>
+        </a:xfrm>
+        <a:prstGeom prst="roundRect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="bg2">
+            <a:lumMod val="90000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr spcFirstLastPara="0" vertOverflow="clip" horzOverflow="clip" wrap="square" lIns="91440" tIns="45720" rIns="91440" bIns="45720" rtlCol="0" anchor="t">
+          <a:noAutofit/>
+        </a:bodyPr>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr marL="0" indent="0" algn="l"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="3600" b="0" i="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="75000"/>
+                  <a:lumOff val="25000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="Aptos Narrow" panose="020B0004020202020204" pitchFamily="34" charset="0"/>
+            </a:rPr>
+            <a:t>ClassRegisterForm</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>352425</xdr:colOff>
+      <xdr:row>13</xdr:row>
+      <xdr:rowOff>19050</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>666750</xdr:colOff>
+      <xdr:row>15</xdr:row>
+      <xdr:rowOff>19050</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="3" name="四角形 6">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B3EF775A-8B5B-4D35-8AF8-CC4DD2E8D833}"/>
+            </a:ext>
+            <a:ext uri="{147F2762-F138-4A5C-976F-8EAC2B608ADB}">
+              <a16:predDERef xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" pred="{585451F5-6F59-4D89-9C42-34BC080AF344}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1724025" y="2619375"/>
+          <a:ext cx="1685925" cy="400050"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr rot="0" spcFirstLastPara="0" vert="horz" wrap="square" lIns="91440" tIns="45720" rIns="91440" bIns="45720" numCol="1" spcCol="0" rtlCol="0" fromWordArt="0" anchor="t" anchorCtr="0" forceAA="0" compatLnSpc="1">
+          <a:prstTxWarp prst="textNoShape">
+            <a:avLst/>
+          </a:prstTxWarp>
+          <a:noAutofit/>
+        </a:bodyPr>
+        <a:lstStyle>
+          <a:lvl1pPr marL="0" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl1pPr>
+          <a:lvl2pPr marL="457200" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl2pPr>
+          <a:lvl3pPr marL="914400" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl3pPr>
+          <a:lvl4pPr marL="1371600" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl4pPr>
+          <a:lvl5pPr marL="1828800" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl5pPr>
+          <a:lvl6pPr marL="2286000" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl6pPr>
+          <a:lvl7pPr marL="2743200" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl7pPr>
+          <a:lvl8pPr marL="3200400" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl8pPr>
+          <a:lvl9pPr marL="3657600" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl9pPr>
+        </a:lstStyle>
+        <a:p>
+          <a:pPr marL="0" indent="0" algn="ctr"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="1600" b="0" i="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="Aptos Narrow" panose="020B0004020202020204" pitchFamily="34" charset="0"/>
+            </a:rPr>
+            <a:t>startYear : int</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>295275</xdr:colOff>
+      <xdr:row>13</xdr:row>
+      <xdr:rowOff>9525</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>381000</xdr:colOff>
+      <xdr:row>15</xdr:row>
+      <xdr:rowOff>9525</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="4" name="四角形 7">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1F383DB0-25A4-4E17-9929-9DB8468DA87D}"/>
+            </a:ext>
+            <a:ext uri="{147F2762-F138-4A5C-976F-8EAC2B608ADB}">
+              <a16:predDERef xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" pred="{B3EF775A-8B5B-4D35-8AF8-CC4DD2E8D833}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="3724275" y="2609850"/>
+          <a:ext cx="2143125" cy="400050"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr rot="0" spcFirstLastPara="0" vert="horz" wrap="square" lIns="91440" tIns="45720" rIns="91440" bIns="45720" numCol="1" spcCol="0" rtlCol="0" fromWordArt="0" anchor="t" anchorCtr="0" forceAA="0" compatLnSpc="1">
+          <a:prstTxWarp prst="textNoShape">
+            <a:avLst/>
+          </a:prstTxWarp>
+          <a:noAutofit/>
+        </a:bodyPr>
+        <a:lstStyle>
+          <a:lvl1pPr marL="0" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl1pPr>
+          <a:lvl2pPr marL="457200" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl2pPr>
+          <a:lvl3pPr marL="914400" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl3pPr>
+          <a:lvl4pPr marL="1371600" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl4pPr>
+          <a:lvl5pPr marL="1828800" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl5pPr>
+          <a:lvl6pPr marL="2286000" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl6pPr>
+          <a:lvl7pPr marL="2743200" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl7pPr>
+          <a:lvl8pPr marL="3200400" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl8pPr>
+          <a:lvl9pPr marL="3657600" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl9pPr>
+        </a:lstStyle>
+        <a:p>
+          <a:pPr marL="0" indent="0" algn="ctr"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="1600" b="0" i="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="Aptos Narrow" panose="020B0004020202020204" pitchFamily="34" charset="0"/>
+            </a:rPr>
+            <a:t>majorName : String</a:t>
           </a:r>
         </a:p>
       </xdr:txBody>
@@ -2104,4 +2940,24 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{098F936B-FE21-4019-86B3-B337203CCEFD}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15.75"/>
+  <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6B811B7F-C323-46C6-8AA7-5CA98A11A5DF}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15.75"/>
+  <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
 </file>
--- a/class_diagram/model/form/manager/成績管理sys_クラス図_model_form_manager.xlsx
+++ b/class_diagram/model/form/manager/成績管理sys_クラス図_model_form_manager.xlsx
@@ -1,19 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29609"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29711"/>
   <workbookPr/>
-  <xr:revisionPtr revIDLastSave="155" documentId="11_3F8216BDF2DCCE836B02CE998F0AE45F5E522874" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{79943971-9108-4909-AC09-B951A49801E4}"/>
+  <xr:revisionPtr revIDLastSave="193" documentId="11_3F8216BDF2DCCE836B02CE998F0AE45F5E522874" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B91F5B3D-6E0C-45B0-8DA0-0D07A11A2FF7}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" firstSheet="3" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" firstSheet="4" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="SubjectSetForm" sheetId="4" r:id="rId1"/>
     <sheet name="SubjectRegisterForm" sheetId="5" r:id="rId2"/>
     <sheet name="MajorSetForm" sheetId="3" r:id="rId3"/>
     <sheet name="MajorRegisterForm" sheetId="2" r:id="rId4"/>
-    <sheet name="ClassSetForm" sheetId="7" r:id="rId5"/>
-    <sheet name="ClassRegisterForm" sheetId="6" r:id="rId6"/>
+    <sheet name="ClassRegisterForm" sheetId="8" r:id="rId5"/>
+    <sheet name="ClassSetForm" sheetId="7" r:id="rId6"/>
+    <sheet name="ClassSubjectAddForm" sheetId="9" r:id="rId7"/>
   </sheets>
   <calcPr calcId="191028"/>
   <extLst>
@@ -1773,7 +1774,7 @@
         <xdr:cNvPr id="2" name="角丸四角形 2">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00C17359-9A90-49BC-BBF4-28A43125B716}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{09D779B9-4B1D-4977-B08F-609180B4D221}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1826,7 +1827,7 @@
               </a:solidFill>
               <a:latin typeface="Aptos Narrow" panose="020B0004020202020204" pitchFamily="34" charset="0"/>
             </a:rPr>
-            <a:t>ClassSetForm</a:t>
+            <a:t>ClassRegisterForm</a:t>
           </a:r>
         </a:p>
       </xdr:txBody>
@@ -1851,10 +1852,10 @@
         <xdr:cNvPr id="3" name="四角形 6">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D0CCD0E6-B287-448C-ADA7-C2A19C1D7F52}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{EB70D079-51A4-48F9-862B-27F623D5B99A}"/>
             </a:ext>
             <a:ext uri="{147F2762-F138-4A5C-976F-8EAC2B608ADB}">
-              <a16:predDERef xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" pred="{00C17359-9A90-49BC-BBF4-28A43125B716}"/>
+              <a16:predDERef xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" pred="{09D779B9-4B1D-4977-B08F-609180B4D221}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -2018,10 +2019,10 @@
         <xdr:cNvPr id="4" name="四角形 7">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9BD32B3E-78C7-4F63-8B98-688F329EB388}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2343A2E2-A3F6-4533-87E2-95B8CB10B31E}"/>
             </a:ext>
             <a:ext uri="{147F2762-F138-4A5C-976F-8EAC2B608ADB}">
-              <a16:predDERef xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" pred="{D0CCD0E6-B287-448C-ADA7-C2A19C1D7F52}"/>
+              <a16:predDERef xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" pred="{EB70D079-51A4-48F9-862B-27F623D5B99A}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -2161,6 +2162,1175 @@
               <a:latin typeface="Aptos Narrow" panose="020B0004020202020204" pitchFamily="34" charset="0"/>
             </a:rPr>
             <a:t>majorName : String</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>657225</xdr:colOff>
+      <xdr:row>13</xdr:row>
+      <xdr:rowOff>19050</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>314325</xdr:colOff>
+      <xdr:row>15</xdr:row>
+      <xdr:rowOff>19050</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="5" name="四角形 4">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{06FBD914-D313-4B6D-8FE7-184FEC41B9D0}"/>
+            </a:ext>
+            <a:ext uri="{147F2762-F138-4A5C-976F-8EAC2B608ADB}">
+              <a16:predDERef xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" pred="{2343A2E2-A3F6-4533-87E2-95B8CB10B31E}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="6143625" y="2619375"/>
+          <a:ext cx="2400300" cy="400050"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr rot="0" spcFirstLastPara="0" vert="horz" wrap="square" lIns="91440" tIns="45720" rIns="91440" bIns="45720" numCol="1" spcCol="0" rtlCol="0" fromWordArt="0" anchor="t" anchorCtr="0" forceAA="0" compatLnSpc="1">
+          <a:prstTxWarp prst="textNoShape">
+            <a:avLst/>
+          </a:prstTxWarp>
+          <a:noAutofit/>
+        </a:bodyPr>
+        <a:lstStyle>
+          <a:lvl1pPr marL="0" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl1pPr>
+          <a:lvl2pPr marL="457200" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl2pPr>
+          <a:lvl3pPr marL="914400" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl3pPr>
+          <a:lvl4pPr marL="1371600" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl4pPr>
+          <a:lvl5pPr marL="1828800" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl5pPr>
+          <a:lvl6pPr marL="2286000" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl6pPr>
+          <a:lvl7pPr marL="2743200" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl7pPr>
+          <a:lvl8pPr marL="3200400" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl8pPr>
+          <a:lvl9pPr marL="3657600" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl9pPr>
+        </a:lstStyle>
+        <a:p>
+          <a:pPr marL="0" indent="0" algn="ctr"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="1600" b="0" i="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="Aptos Narrow" panose="020B0004020202020204" pitchFamily="34" charset="0"/>
+            </a:rPr>
+            <a:t>subjectNameOne : String</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>485775</xdr:colOff>
+      <xdr:row>13</xdr:row>
+      <xdr:rowOff>9525</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>142875</xdr:colOff>
+      <xdr:row>15</xdr:row>
+      <xdr:rowOff>9525</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="6" name="四角形 5">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7669963C-F11B-487D-8D36-4D0E53B34135}"/>
+            </a:ext>
+            <a:ext uri="{147F2762-F138-4A5C-976F-8EAC2B608ADB}">
+              <a16:predDERef xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" pred="{06FBD914-D313-4B6D-8FE7-184FEC41B9D0}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="8715375" y="2609850"/>
+          <a:ext cx="2400300" cy="400050"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr rot="0" spcFirstLastPara="0" vert="horz" wrap="square" lIns="91440" tIns="45720" rIns="91440" bIns="45720" numCol="1" spcCol="0" rtlCol="0" fromWordArt="0" anchor="t" anchorCtr="0" forceAA="0" compatLnSpc="1">
+          <a:prstTxWarp prst="textNoShape">
+            <a:avLst/>
+          </a:prstTxWarp>
+          <a:noAutofit/>
+        </a:bodyPr>
+        <a:lstStyle>
+          <a:lvl1pPr marL="0" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl1pPr>
+          <a:lvl2pPr marL="457200" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl2pPr>
+          <a:lvl3pPr marL="914400" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl3pPr>
+          <a:lvl4pPr marL="1371600" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl4pPr>
+          <a:lvl5pPr marL="1828800" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl5pPr>
+          <a:lvl6pPr marL="2286000" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl6pPr>
+          <a:lvl7pPr marL="2743200" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl7pPr>
+          <a:lvl8pPr marL="3200400" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl8pPr>
+          <a:lvl9pPr marL="3657600" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl9pPr>
+        </a:lstStyle>
+        <a:p>
+          <a:pPr marL="0" indent="0" algn="ctr"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="1600" b="0" i="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="Aptos Narrow" panose="020B0004020202020204" pitchFamily="34" charset="0"/>
+            </a:rPr>
+            <a:t>subjectNameTwo : String</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>161925</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>66675</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>504825</xdr:colOff>
+      <xdr:row>18</xdr:row>
+      <xdr:rowOff>66675</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="7" name="四角形 6">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5CBF4696-2A17-45F6-8558-6F21EAC5D35A}"/>
+            </a:ext>
+            <a:ext uri="{147F2762-F138-4A5C-976F-8EAC2B608ADB}">
+              <a16:predDERef xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" pred="{7669963C-F11B-487D-8D36-4D0E53B34135}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="847725" y="3267075"/>
+          <a:ext cx="2400300" cy="400050"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr rot="0" spcFirstLastPara="0" vert="horz" wrap="square" lIns="91440" tIns="45720" rIns="91440" bIns="45720" numCol="1" spcCol="0" rtlCol="0" fromWordArt="0" anchor="t" anchorCtr="0" forceAA="0" compatLnSpc="1">
+          <a:prstTxWarp prst="textNoShape">
+            <a:avLst/>
+          </a:prstTxWarp>
+          <a:noAutofit/>
+        </a:bodyPr>
+        <a:lstStyle>
+          <a:lvl1pPr marL="0" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl1pPr>
+          <a:lvl2pPr marL="457200" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl2pPr>
+          <a:lvl3pPr marL="914400" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl3pPr>
+          <a:lvl4pPr marL="1371600" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl4pPr>
+          <a:lvl5pPr marL="1828800" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl5pPr>
+          <a:lvl6pPr marL="2286000" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl6pPr>
+          <a:lvl7pPr marL="2743200" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl7pPr>
+          <a:lvl8pPr marL="3200400" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl8pPr>
+          <a:lvl9pPr marL="3657600" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl9pPr>
+        </a:lstStyle>
+        <a:p>
+          <a:pPr marL="0" indent="0" algn="ctr"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="1600" b="0" i="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="Aptos Narrow" panose="020B0004020202020204" pitchFamily="34" charset="0"/>
+            </a:rPr>
+            <a:t>subjectNameThree : String</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>28575</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>57150</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>371475</xdr:colOff>
+      <xdr:row>18</xdr:row>
+      <xdr:rowOff>57150</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="8" name="四角形 7">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5E462F47-C96F-43A7-BFAA-3427BE38A066}"/>
+            </a:ext>
+            <a:ext uri="{147F2762-F138-4A5C-976F-8EAC2B608ADB}">
+              <a16:predDERef xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" pred="{5CBF4696-2A17-45F6-8558-6F21EAC5D35A}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="3457575" y="3257550"/>
+          <a:ext cx="2400300" cy="400050"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr rot="0" spcFirstLastPara="0" vert="horz" wrap="square" lIns="91440" tIns="45720" rIns="91440" bIns="45720" numCol="1" spcCol="0" rtlCol="0" fromWordArt="0" anchor="t" anchorCtr="0" forceAA="0" compatLnSpc="1">
+          <a:prstTxWarp prst="textNoShape">
+            <a:avLst/>
+          </a:prstTxWarp>
+          <a:noAutofit/>
+        </a:bodyPr>
+        <a:lstStyle>
+          <a:lvl1pPr marL="0" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl1pPr>
+          <a:lvl2pPr marL="457200" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl2pPr>
+          <a:lvl3pPr marL="914400" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl3pPr>
+          <a:lvl4pPr marL="1371600" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl4pPr>
+          <a:lvl5pPr marL="1828800" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl5pPr>
+          <a:lvl6pPr marL="2286000" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl6pPr>
+          <a:lvl7pPr marL="2743200" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl7pPr>
+          <a:lvl8pPr marL="3200400" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl8pPr>
+          <a:lvl9pPr marL="3657600" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl9pPr>
+        </a:lstStyle>
+        <a:p>
+          <a:pPr marL="0" indent="0" algn="ctr"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="1600" b="0" i="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="Aptos Narrow" panose="020B0004020202020204" pitchFamily="34" charset="0"/>
+            </a:rPr>
+            <a:t>subjectNameFour : String</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>523875</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>47625</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>180975</xdr:colOff>
+      <xdr:row>18</xdr:row>
+      <xdr:rowOff>47625</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="9" name="四角形 8">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{14BDC180-0356-4680-A62E-730D8EE84845}"/>
+            </a:ext>
+            <a:ext uri="{147F2762-F138-4A5C-976F-8EAC2B608ADB}">
+              <a16:predDERef xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" pred="{5E462F47-C96F-43A7-BFAA-3427BE38A066}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="6010275" y="3248025"/>
+          <a:ext cx="2400300" cy="400050"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr rot="0" spcFirstLastPara="0" vert="horz" wrap="square" lIns="91440" tIns="45720" rIns="91440" bIns="45720" numCol="1" spcCol="0" rtlCol="0" fromWordArt="0" anchor="t" anchorCtr="0" forceAA="0" compatLnSpc="1">
+          <a:prstTxWarp prst="textNoShape">
+            <a:avLst/>
+          </a:prstTxWarp>
+          <a:noAutofit/>
+        </a:bodyPr>
+        <a:lstStyle>
+          <a:lvl1pPr marL="0" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl1pPr>
+          <a:lvl2pPr marL="457200" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl2pPr>
+          <a:lvl3pPr marL="914400" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl3pPr>
+          <a:lvl4pPr marL="1371600" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl4pPr>
+          <a:lvl5pPr marL="1828800" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl5pPr>
+          <a:lvl6pPr marL="2286000" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl6pPr>
+          <a:lvl7pPr marL="2743200" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl7pPr>
+          <a:lvl8pPr marL="3200400" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl8pPr>
+          <a:lvl9pPr marL="3657600" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl9pPr>
+        </a:lstStyle>
+        <a:p>
+          <a:pPr marL="0" indent="0" algn="ctr"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="1600" b="0" i="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="Aptos Narrow" panose="020B0004020202020204" pitchFamily="34" charset="0"/>
+            </a:rPr>
+            <a:t>subjectNameFive : String</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>304800</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>38100</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>647700</xdr:colOff>
+      <xdr:row>18</xdr:row>
+      <xdr:rowOff>38100</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="10" name="四角形 9">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8A1CF877-40FA-49A4-8E57-91168C2BED9F}"/>
+            </a:ext>
+            <a:ext uri="{147F2762-F138-4A5C-976F-8EAC2B608ADB}">
+              <a16:predDERef xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" pred="{14BDC180-0356-4680-A62E-730D8EE84845}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="8534400" y="3238500"/>
+          <a:ext cx="2400300" cy="400050"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr rot="0" spcFirstLastPara="0" vert="horz" wrap="square" lIns="91440" tIns="45720" rIns="91440" bIns="45720" numCol="1" spcCol="0" rtlCol="0" fromWordArt="0" anchor="t" anchorCtr="0" forceAA="0" compatLnSpc="1">
+          <a:prstTxWarp prst="textNoShape">
+            <a:avLst/>
+          </a:prstTxWarp>
+          <a:noAutofit/>
+        </a:bodyPr>
+        <a:lstStyle>
+          <a:lvl1pPr marL="0" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl1pPr>
+          <a:lvl2pPr marL="457200" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl2pPr>
+          <a:lvl3pPr marL="914400" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl3pPr>
+          <a:lvl4pPr marL="1371600" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl4pPr>
+          <a:lvl5pPr marL="1828800" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl5pPr>
+          <a:lvl6pPr marL="2286000" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl6pPr>
+          <a:lvl7pPr marL="2743200" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl7pPr>
+          <a:lvl8pPr marL="3200400" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl8pPr>
+          <a:lvl9pPr marL="3657600" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl9pPr>
+        </a:lstStyle>
+        <a:p>
+          <a:pPr marL="0" indent="0" algn="ctr"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="1600" b="0" i="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="Aptos Narrow" panose="020B0004020202020204" pitchFamily="34" charset="0"/>
+            </a:rPr>
+            <a:t>subjectNameSix : String</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>304800</xdr:colOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>19050</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>647700</xdr:colOff>
+      <xdr:row>21</xdr:row>
+      <xdr:rowOff>19050</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="11" name="四角形 10">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{EC7DFDC4-55CB-4F5F-8EFA-63F84D5BAE4F}"/>
+            </a:ext>
+            <a:ext uri="{147F2762-F138-4A5C-976F-8EAC2B608ADB}">
+              <a16:predDERef xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" pred="{8A1CF877-40FA-49A4-8E57-91168C2BED9F}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="990600" y="3819525"/>
+          <a:ext cx="2400300" cy="400050"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr rot="0" spcFirstLastPara="0" vert="horz" wrap="square" lIns="91440" tIns="45720" rIns="91440" bIns="45720" numCol="1" spcCol="0" rtlCol="0" fromWordArt="0" anchor="t" anchorCtr="0" forceAA="0" compatLnSpc="1">
+          <a:prstTxWarp prst="textNoShape">
+            <a:avLst/>
+          </a:prstTxWarp>
+          <a:noAutofit/>
+        </a:bodyPr>
+        <a:lstStyle>
+          <a:lvl1pPr marL="0" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl1pPr>
+          <a:lvl2pPr marL="457200" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl2pPr>
+          <a:lvl3pPr marL="914400" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl3pPr>
+          <a:lvl4pPr marL="1371600" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl4pPr>
+          <a:lvl5pPr marL="1828800" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl5pPr>
+          <a:lvl6pPr marL="2286000" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl6pPr>
+          <a:lvl7pPr marL="2743200" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl7pPr>
+          <a:lvl8pPr marL="3200400" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl8pPr>
+          <a:lvl9pPr marL="3657600" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl9pPr>
+        </a:lstStyle>
+        <a:p>
+          <a:pPr marL="0" indent="0" algn="ctr"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="1600" b="0" i="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="Aptos Narrow" panose="020B0004020202020204" pitchFamily="34" charset="0"/>
+            </a:rPr>
+            <a:t>subjectNameSeven : String</a:t>
           </a:r>
         </a:p>
       </xdr:txBody>
@@ -2190,7 +3360,7 @@
         <xdr:cNvPr id="2" name="角丸四角形 2">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{585451F5-6F59-4D89-9C42-34BC080AF344}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00C17359-9A90-49BC-BBF4-28A43125B716}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -2243,7 +3413,7 @@
               </a:solidFill>
               <a:latin typeface="Aptos Narrow" panose="020B0004020202020204" pitchFamily="34" charset="0"/>
             </a:rPr>
-            <a:t>ClassRegisterForm</a:t>
+            <a:t>ClassSetForm</a:t>
           </a:r>
         </a:p>
       </xdr:txBody>
@@ -2268,10 +3438,10 @@
         <xdr:cNvPr id="3" name="四角形 6">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B3EF775A-8B5B-4D35-8AF8-CC4DD2E8D833}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D0CCD0E6-B287-448C-ADA7-C2A19C1D7F52}"/>
             </a:ext>
             <a:ext uri="{147F2762-F138-4A5C-976F-8EAC2B608ADB}">
-              <a16:predDERef xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" pred="{585451F5-6F59-4D89-9C42-34BC080AF344}"/>
+              <a16:predDERef xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" pred="{00C17359-9A90-49BC-BBF4-28A43125B716}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -2435,10 +3605,10 @@
         <xdr:cNvPr id="4" name="四角形 7">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1F383DB0-25A4-4E17-9929-9DB8468DA87D}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9BD32B3E-78C7-4F63-8B98-688F329EB388}"/>
             </a:ext>
             <a:ext uri="{147F2762-F138-4A5C-976F-8EAC2B608ADB}">
-              <a16:predDERef xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" pred="{B3EF775A-8B5B-4D35-8AF8-CC4DD2E8D833}"/>
+              <a16:predDERef xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" pred="{D0CCD0E6-B287-448C-ADA7-C2A19C1D7F52}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -2578,6 +3748,1759 @@
               <a:latin typeface="Aptos Narrow" panose="020B0004020202020204" pitchFamily="34" charset="0"/>
             </a:rPr>
             <a:t>majorName : String</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>657225</xdr:colOff>
+      <xdr:row>13</xdr:row>
+      <xdr:rowOff>19050</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>314325</xdr:colOff>
+      <xdr:row>15</xdr:row>
+      <xdr:rowOff>19050</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="5" name="四角形 4">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{349D591F-666F-4840-BB09-17ECFDB3BADC}"/>
+            </a:ext>
+            <a:ext uri="{147F2762-F138-4A5C-976F-8EAC2B608ADB}">
+              <a16:predDERef xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" pred="{9BD32B3E-78C7-4F63-8B98-688F329EB388}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="6143625" y="2619375"/>
+          <a:ext cx="2400300" cy="400050"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr rot="0" spcFirstLastPara="0" vert="horz" wrap="square" lIns="91440" tIns="45720" rIns="91440" bIns="45720" numCol="1" spcCol="0" rtlCol="0" fromWordArt="0" anchor="t" anchorCtr="0" forceAA="0" compatLnSpc="1">
+          <a:prstTxWarp prst="textNoShape">
+            <a:avLst/>
+          </a:prstTxWarp>
+          <a:noAutofit/>
+        </a:bodyPr>
+        <a:lstStyle>
+          <a:lvl1pPr marL="0" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl1pPr>
+          <a:lvl2pPr marL="457200" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl2pPr>
+          <a:lvl3pPr marL="914400" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl3pPr>
+          <a:lvl4pPr marL="1371600" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl4pPr>
+          <a:lvl5pPr marL="1828800" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl5pPr>
+          <a:lvl6pPr marL="2286000" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl6pPr>
+          <a:lvl7pPr marL="2743200" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl7pPr>
+          <a:lvl8pPr marL="3200400" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl8pPr>
+          <a:lvl9pPr marL="3657600" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl9pPr>
+        </a:lstStyle>
+        <a:p>
+          <a:pPr marL="0" indent="0" algn="ctr"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="1600" b="0" i="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="Aptos Narrow" panose="020B0004020202020204" pitchFamily="34" charset="0"/>
+            </a:rPr>
+            <a:t>subjectNameOne : String</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>485775</xdr:colOff>
+      <xdr:row>13</xdr:row>
+      <xdr:rowOff>9525</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>142875</xdr:colOff>
+      <xdr:row>15</xdr:row>
+      <xdr:rowOff>9525</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="6" name="四角形 5">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{AE8AE018-A8A7-4F04-B62B-51933286725F}"/>
+            </a:ext>
+            <a:ext uri="{147F2762-F138-4A5C-976F-8EAC2B608ADB}">
+              <a16:predDERef xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" pred="{349D591F-666F-4840-BB09-17ECFDB3BADC}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="8715375" y="2609850"/>
+          <a:ext cx="2400300" cy="400050"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr rot="0" spcFirstLastPara="0" vert="horz" wrap="square" lIns="91440" tIns="45720" rIns="91440" bIns="45720" numCol="1" spcCol="0" rtlCol="0" fromWordArt="0" anchor="t" anchorCtr="0" forceAA="0" compatLnSpc="1">
+          <a:prstTxWarp prst="textNoShape">
+            <a:avLst/>
+          </a:prstTxWarp>
+          <a:noAutofit/>
+        </a:bodyPr>
+        <a:lstStyle>
+          <a:lvl1pPr marL="0" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl1pPr>
+          <a:lvl2pPr marL="457200" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl2pPr>
+          <a:lvl3pPr marL="914400" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl3pPr>
+          <a:lvl4pPr marL="1371600" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl4pPr>
+          <a:lvl5pPr marL="1828800" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl5pPr>
+          <a:lvl6pPr marL="2286000" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl6pPr>
+          <a:lvl7pPr marL="2743200" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl7pPr>
+          <a:lvl8pPr marL="3200400" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl8pPr>
+          <a:lvl9pPr marL="3657600" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl9pPr>
+        </a:lstStyle>
+        <a:p>
+          <a:pPr marL="0" indent="0" algn="ctr"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="1600" b="0" i="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="Aptos Narrow" panose="020B0004020202020204" pitchFamily="34" charset="0"/>
+            </a:rPr>
+            <a:t>subjectNameTwo : String</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>161925</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>66675</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>504825</xdr:colOff>
+      <xdr:row>18</xdr:row>
+      <xdr:rowOff>66675</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="7" name="四角形 6">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9B9826D8-CE03-49D8-95A1-45A3AAA37D15}"/>
+            </a:ext>
+            <a:ext uri="{147F2762-F138-4A5C-976F-8EAC2B608ADB}">
+              <a16:predDERef xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" pred="{AE8AE018-A8A7-4F04-B62B-51933286725F}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="847725" y="3267075"/>
+          <a:ext cx="2400300" cy="400050"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr rot="0" spcFirstLastPara="0" vert="horz" wrap="square" lIns="91440" tIns="45720" rIns="91440" bIns="45720" numCol="1" spcCol="0" rtlCol="0" fromWordArt="0" anchor="t" anchorCtr="0" forceAA="0" compatLnSpc="1">
+          <a:prstTxWarp prst="textNoShape">
+            <a:avLst/>
+          </a:prstTxWarp>
+          <a:noAutofit/>
+        </a:bodyPr>
+        <a:lstStyle>
+          <a:lvl1pPr marL="0" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl1pPr>
+          <a:lvl2pPr marL="457200" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl2pPr>
+          <a:lvl3pPr marL="914400" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl3pPr>
+          <a:lvl4pPr marL="1371600" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl4pPr>
+          <a:lvl5pPr marL="1828800" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl5pPr>
+          <a:lvl6pPr marL="2286000" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl6pPr>
+          <a:lvl7pPr marL="2743200" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl7pPr>
+          <a:lvl8pPr marL="3200400" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl8pPr>
+          <a:lvl9pPr marL="3657600" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl9pPr>
+        </a:lstStyle>
+        <a:p>
+          <a:pPr marL="0" indent="0" algn="ctr"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="1600" b="0" i="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="Aptos Narrow" panose="020B0004020202020204" pitchFamily="34" charset="0"/>
+            </a:rPr>
+            <a:t>subjectNameThree : String</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>28575</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>57150</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>371475</xdr:colOff>
+      <xdr:row>18</xdr:row>
+      <xdr:rowOff>57150</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="8" name="四角形 7">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3C161718-F1F3-4544-A6A0-AEECB6ED7A95}"/>
+            </a:ext>
+            <a:ext uri="{147F2762-F138-4A5C-976F-8EAC2B608ADB}">
+              <a16:predDERef xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" pred="{9B9826D8-CE03-49D8-95A1-45A3AAA37D15}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="3457575" y="3257550"/>
+          <a:ext cx="2400300" cy="400050"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr rot="0" spcFirstLastPara="0" vert="horz" wrap="square" lIns="91440" tIns="45720" rIns="91440" bIns="45720" numCol="1" spcCol="0" rtlCol="0" fromWordArt="0" anchor="t" anchorCtr="0" forceAA="0" compatLnSpc="1">
+          <a:prstTxWarp prst="textNoShape">
+            <a:avLst/>
+          </a:prstTxWarp>
+          <a:noAutofit/>
+        </a:bodyPr>
+        <a:lstStyle>
+          <a:lvl1pPr marL="0" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl1pPr>
+          <a:lvl2pPr marL="457200" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl2pPr>
+          <a:lvl3pPr marL="914400" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl3pPr>
+          <a:lvl4pPr marL="1371600" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl4pPr>
+          <a:lvl5pPr marL="1828800" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl5pPr>
+          <a:lvl6pPr marL="2286000" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl6pPr>
+          <a:lvl7pPr marL="2743200" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl7pPr>
+          <a:lvl8pPr marL="3200400" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl8pPr>
+          <a:lvl9pPr marL="3657600" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl9pPr>
+        </a:lstStyle>
+        <a:p>
+          <a:pPr marL="0" indent="0" algn="ctr"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="1600" b="0" i="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="Aptos Narrow" panose="020B0004020202020204" pitchFamily="34" charset="0"/>
+            </a:rPr>
+            <a:t>subjectNameFour : String</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>523875</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>47625</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>180975</xdr:colOff>
+      <xdr:row>18</xdr:row>
+      <xdr:rowOff>47625</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="9" name="四角形 8">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{22AC36E0-6F75-42E6-9C3D-788950E79B42}"/>
+            </a:ext>
+            <a:ext uri="{147F2762-F138-4A5C-976F-8EAC2B608ADB}">
+              <a16:predDERef xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" pred="{3C161718-F1F3-4544-A6A0-AEECB6ED7A95}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="6010275" y="3248025"/>
+          <a:ext cx="2400300" cy="400050"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr rot="0" spcFirstLastPara="0" vert="horz" wrap="square" lIns="91440" tIns="45720" rIns="91440" bIns="45720" numCol="1" spcCol="0" rtlCol="0" fromWordArt="0" anchor="t" anchorCtr="0" forceAA="0" compatLnSpc="1">
+          <a:prstTxWarp prst="textNoShape">
+            <a:avLst/>
+          </a:prstTxWarp>
+          <a:noAutofit/>
+        </a:bodyPr>
+        <a:lstStyle>
+          <a:lvl1pPr marL="0" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl1pPr>
+          <a:lvl2pPr marL="457200" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl2pPr>
+          <a:lvl3pPr marL="914400" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl3pPr>
+          <a:lvl4pPr marL="1371600" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl4pPr>
+          <a:lvl5pPr marL="1828800" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl5pPr>
+          <a:lvl6pPr marL="2286000" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl6pPr>
+          <a:lvl7pPr marL="2743200" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl7pPr>
+          <a:lvl8pPr marL="3200400" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl8pPr>
+          <a:lvl9pPr marL="3657600" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl9pPr>
+        </a:lstStyle>
+        <a:p>
+          <a:pPr marL="0" indent="0" algn="ctr"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="1600" b="0" i="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="Aptos Narrow" panose="020B0004020202020204" pitchFamily="34" charset="0"/>
+            </a:rPr>
+            <a:t>subjectNameFive : String</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>304800</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>38100</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>647700</xdr:colOff>
+      <xdr:row>18</xdr:row>
+      <xdr:rowOff>38100</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="10" name="四角形 9">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{053AE681-CD40-44C3-ACC7-4F1AD78D8927}"/>
+            </a:ext>
+            <a:ext uri="{147F2762-F138-4A5C-976F-8EAC2B608ADB}">
+              <a16:predDERef xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" pred="{22AC36E0-6F75-42E6-9C3D-788950E79B42}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="8534400" y="3238500"/>
+          <a:ext cx="2400300" cy="400050"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr rot="0" spcFirstLastPara="0" vert="horz" wrap="square" lIns="91440" tIns="45720" rIns="91440" bIns="45720" numCol="1" spcCol="0" rtlCol="0" fromWordArt="0" anchor="t" anchorCtr="0" forceAA="0" compatLnSpc="1">
+          <a:prstTxWarp prst="textNoShape">
+            <a:avLst/>
+          </a:prstTxWarp>
+          <a:noAutofit/>
+        </a:bodyPr>
+        <a:lstStyle>
+          <a:lvl1pPr marL="0" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl1pPr>
+          <a:lvl2pPr marL="457200" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl2pPr>
+          <a:lvl3pPr marL="914400" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl3pPr>
+          <a:lvl4pPr marL="1371600" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl4pPr>
+          <a:lvl5pPr marL="1828800" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl5pPr>
+          <a:lvl6pPr marL="2286000" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl6pPr>
+          <a:lvl7pPr marL="2743200" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl7pPr>
+          <a:lvl8pPr marL="3200400" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl8pPr>
+          <a:lvl9pPr marL="3657600" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl9pPr>
+        </a:lstStyle>
+        <a:p>
+          <a:pPr marL="0" indent="0" algn="ctr"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="1600" b="0" i="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="Aptos Narrow" panose="020B0004020202020204" pitchFamily="34" charset="0"/>
+            </a:rPr>
+            <a:t>subjectNameSix : String</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>304800</xdr:colOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>19050</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>647700</xdr:colOff>
+      <xdr:row>21</xdr:row>
+      <xdr:rowOff>19050</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="11" name="四角形 10">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{CAB12E78-B4B0-40B2-8903-1D7EDF52ABE7}"/>
+            </a:ext>
+            <a:ext uri="{147F2762-F138-4A5C-976F-8EAC2B608ADB}">
+              <a16:predDERef xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" pred="{053AE681-CD40-44C3-ACC7-4F1AD78D8927}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="990600" y="3819525"/>
+          <a:ext cx="2400300" cy="400050"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr rot="0" spcFirstLastPara="0" vert="horz" wrap="square" lIns="91440" tIns="45720" rIns="91440" bIns="45720" numCol="1" spcCol="0" rtlCol="0" fromWordArt="0" anchor="t" anchorCtr="0" forceAA="0" compatLnSpc="1">
+          <a:prstTxWarp prst="textNoShape">
+            <a:avLst/>
+          </a:prstTxWarp>
+          <a:noAutofit/>
+        </a:bodyPr>
+        <a:lstStyle>
+          <a:lvl1pPr marL="0" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl1pPr>
+          <a:lvl2pPr marL="457200" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl2pPr>
+          <a:lvl3pPr marL="914400" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl3pPr>
+          <a:lvl4pPr marL="1371600" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl4pPr>
+          <a:lvl5pPr marL="1828800" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl5pPr>
+          <a:lvl6pPr marL="2286000" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl6pPr>
+          <a:lvl7pPr marL="2743200" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl7pPr>
+          <a:lvl8pPr marL="3200400" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl8pPr>
+          <a:lvl9pPr marL="3657600" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl9pPr>
+        </a:lstStyle>
+        <a:p>
+          <a:pPr marL="0" indent="0" algn="ctr"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="1600" b="0" i="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="Aptos Narrow" panose="020B0004020202020204" pitchFamily="34" charset="0"/>
+            </a:rPr>
+            <a:t>subjectNameSeven : String</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing7.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>676275</xdr:colOff>
+      <xdr:row>5</xdr:row>
+      <xdr:rowOff>104775</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>17</xdr:col>
+      <xdr:colOff>114300</xdr:colOff>
+      <xdr:row>21</xdr:row>
+      <xdr:rowOff>161925</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="2" name="角丸四角形 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{53937BF3-3319-44E3-9E6F-C716A76A5254}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="676275" y="1104900"/>
+          <a:ext cx="11096625" cy="3257550"/>
+        </a:xfrm>
+        <a:prstGeom prst="roundRect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="bg2">
+            <a:lumMod val="90000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr spcFirstLastPara="0" vertOverflow="clip" horzOverflow="clip" wrap="square" lIns="91440" tIns="45720" rIns="91440" bIns="45720" rtlCol="0" anchor="t">
+          <a:noAutofit/>
+        </a:bodyPr>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr marL="0" indent="0" algn="l"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="3600" b="0" i="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="75000"/>
+                  <a:lumOff val="25000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="Aptos Narrow" panose="020B0004020202020204" pitchFamily="34" charset="0"/>
+            </a:rPr>
+            <a:t>ClassSubjectAddForm</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>352425</xdr:colOff>
+      <xdr:row>13</xdr:row>
+      <xdr:rowOff>19050</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>666750</xdr:colOff>
+      <xdr:row>15</xdr:row>
+      <xdr:rowOff>19050</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="3" name="四角形 6">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6400A100-8569-424F-97FA-9E923B436774}"/>
+            </a:ext>
+            <a:ext uri="{147F2762-F138-4A5C-976F-8EAC2B608ADB}">
+              <a16:predDERef xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" pred="{53937BF3-3319-44E3-9E6F-C716A76A5254}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1724025" y="2619375"/>
+          <a:ext cx="1685925" cy="400050"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr rot="0" spcFirstLastPara="0" vert="horz" wrap="square" lIns="91440" tIns="45720" rIns="91440" bIns="45720" numCol="1" spcCol="0" rtlCol="0" fromWordArt="0" anchor="t" anchorCtr="0" forceAA="0" compatLnSpc="1">
+          <a:prstTxWarp prst="textNoShape">
+            <a:avLst/>
+          </a:prstTxWarp>
+          <a:noAutofit/>
+        </a:bodyPr>
+        <a:lstStyle>
+          <a:lvl1pPr marL="0" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl1pPr>
+          <a:lvl2pPr marL="457200" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl2pPr>
+          <a:lvl3pPr marL="914400" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl3pPr>
+          <a:lvl4pPr marL="1371600" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl4pPr>
+          <a:lvl5pPr marL="1828800" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl5pPr>
+          <a:lvl6pPr marL="2286000" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl6pPr>
+          <a:lvl7pPr marL="2743200" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl7pPr>
+          <a:lvl8pPr marL="3200400" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl8pPr>
+          <a:lvl9pPr marL="3657600" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl9pPr>
+        </a:lstStyle>
+        <a:p>
+          <a:pPr marL="0" indent="0" algn="ctr"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="1600" b="0" i="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="Aptos Narrow" panose="020B0004020202020204" pitchFamily="34" charset="0"/>
+            </a:rPr>
+            <a:t>classId : int</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>142875</xdr:colOff>
+      <xdr:row>13</xdr:row>
+      <xdr:rowOff>38100</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>457200</xdr:colOff>
+      <xdr:row>15</xdr:row>
+      <xdr:rowOff>38100</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="12" name="四角形 11">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{06F3ECE5-C8AA-4EB7-A633-B18A488F2102}"/>
+            </a:ext>
+            <a:ext uri="{147F2762-F138-4A5C-976F-8EAC2B608ADB}">
+              <a16:predDERef xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" pred="{6400A100-8569-424F-97FA-9E923B436774}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="3571875" y="2638425"/>
+          <a:ext cx="1685925" cy="400050"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr rot="0" spcFirstLastPara="0" vert="horz" wrap="square" lIns="91440" tIns="45720" rIns="91440" bIns="45720" numCol="1" spcCol="0" rtlCol="0" fromWordArt="0" anchor="t" anchorCtr="0" forceAA="0" compatLnSpc="1">
+          <a:prstTxWarp prst="textNoShape">
+            <a:avLst/>
+          </a:prstTxWarp>
+          <a:noAutofit/>
+        </a:bodyPr>
+        <a:lstStyle>
+          <a:lvl1pPr marL="0" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl1pPr>
+          <a:lvl2pPr marL="457200" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl2pPr>
+          <a:lvl3pPr marL="914400" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl3pPr>
+          <a:lvl4pPr marL="1371600" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl4pPr>
+          <a:lvl5pPr marL="1828800" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl5pPr>
+          <a:lvl6pPr marL="2286000" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl6pPr>
+          <a:lvl7pPr marL="2743200" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl7pPr>
+          <a:lvl8pPr marL="3200400" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl8pPr>
+          <a:lvl9pPr marL="3657600" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl9pPr>
+        </a:lstStyle>
+        <a:p>
+          <a:pPr marL="0" indent="0" algn="ctr"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="1600" b="0" i="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="Aptos Narrow" panose="020B0004020202020204" pitchFamily="34" charset="0"/>
+            </a:rPr>
+            <a:t>subjectId : int</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>590550</xdr:colOff>
+      <xdr:row>13</xdr:row>
+      <xdr:rowOff>38100</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>219075</xdr:colOff>
+      <xdr:row>15</xdr:row>
+      <xdr:rowOff>38100</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="13" name="四角形 12">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A679812B-7894-4982-916E-2F404402EE18}"/>
+            </a:ext>
+            <a:ext uri="{147F2762-F138-4A5C-976F-8EAC2B608ADB}">
+              <a16:predDERef xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" pred="{06F3ECE5-C8AA-4EB7-A633-B18A488F2102}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="5391150" y="2638425"/>
+          <a:ext cx="1685925" cy="400050"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr rot="0" spcFirstLastPara="0" vert="horz" wrap="square" lIns="91440" tIns="45720" rIns="91440" bIns="45720" numCol="1" spcCol="0" rtlCol="0" fromWordArt="0" anchor="t" anchorCtr="0" forceAA="0" compatLnSpc="1">
+          <a:prstTxWarp prst="textNoShape">
+            <a:avLst/>
+          </a:prstTxWarp>
+          <a:noAutofit/>
+        </a:bodyPr>
+        <a:lstStyle>
+          <a:lvl1pPr marL="0" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl1pPr>
+          <a:lvl2pPr marL="457200" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl2pPr>
+          <a:lvl3pPr marL="914400" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl3pPr>
+          <a:lvl4pPr marL="1371600" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl4pPr>
+          <a:lvl5pPr marL="1828800" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl5pPr>
+          <a:lvl6pPr marL="2286000" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl6pPr>
+          <a:lvl7pPr marL="2743200" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl7pPr>
+          <a:lvl8pPr marL="3200400" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl8pPr>
+          <a:lvl9pPr marL="3657600" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl9pPr>
+        </a:lstStyle>
+        <a:p>
+          <a:pPr marL="0" indent="0" algn="ctr"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="1600" b="0" i="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="Aptos Narrow" panose="020B0004020202020204" pitchFamily="34" charset="0"/>
+            </a:rPr>
+            <a:t>managerId : int</a:t>
           </a:r>
         </a:p>
       </xdr:txBody>
@@ -2943,6 +5866,16 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9948EC00-2DD0-4A65-86C9-D4FA32DEDC13}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15.75"/>
+  <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{098F936B-FE21-4019-86B3-B337203CCEFD}">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="15.75"/>
@@ -2952,8 +5885,8 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6B811B7F-C323-46C6-8AA7-5CA98A11A5DF}">
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{56270AF7-936D-4AD4-B43E-5582D07FF799}">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="15.75"/>
   <sheetData/>
